--- a/assets/constructions/examples/ctd_tsmb_tupleface_groove.xlsx
+++ b/assets/constructions/examples/ctd_tsmb_tupleface_groove.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,11 +644,36 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>8.0SIR2.15AD471/472-2.8VMX</t>
+          <t>10.0SIR1.6AD471/472-2.3VMX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -668,13 +693,13 @@
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>10.44</v>
+        <v>12.44</v>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
-        <v>10.44</v>
+        <v>12.44</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
@@ -694,20 +719,20 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>3.95</v>
+        <v>4.95</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="n">
@@ -725,7 +750,7 @@
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>VARGUS_8SI02</t>
+          <t>VARGUS_10SI02</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -767,13 +792,32 @@
       <c r="AQ2" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>18850.82</v>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>6.0SIR1.6AD471/472-2.3VMX</t>
+          <t>8.0SIR1.3AD471/472-2.0VMX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -793,13 +837,13 @@
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="G3" t="n">
         <v>8</v>
       </c>
-      <c r="G3" t="n">
-        <v>6</v>
-      </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>10.44</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
@@ -819,20 +863,20 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>1.9</v>
+        <v>3.95</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
@@ -850,7 +894,7 @@
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_8SI02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -892,13 +936,32 @@
       <c r="AQ3" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>173.8</v>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>15274</v>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6.0SIR1.85AD471/472-2.5VMX</t>
+          <t>10.0SIR2.15AD471/472-2.8VMX</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -918,13 +981,13 @@
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>8.199999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4" t="n">
-        <v>8.199999999999999</v>
+        <v>12.44</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
@@ -944,20 +1007,20 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>1.9</v>
+        <v>4.95</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="n">
@@ -975,7 +1038,7 @@
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_10SI02</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1017,13 +1080,32 @@
       <c r="AQ4" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>18850.82</v>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6.0SIR2.15AD471/472-2.8VMX</t>
+          <t>10.0SIR1.85AD471/472-2.5VMX</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1043,13 +1125,13 @@
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>8.5</v>
+        <v>12.44</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" t="n">
-        <v>8.5</v>
+        <v>12.44</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
@@ -1069,20 +1151,20 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>1.9</v>
+        <v>4.95</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="T5" t="n">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="n">
@@ -1100,7 +1182,7 @@
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>VARGUS_6SI02</t>
+          <t>VARGUS_10SI02</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -1142,13 +1224,32 @@
       <c r="AQ5" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>214.5</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>18850.82</v>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>8.0SIR2.65AD471/472-3.3VMX</t>
+          <t>6.0SIR1.1AD471/472-1.8VMX</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1168,13 +1269,13 @@
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>10.44</v>
+        <v>7.5</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>10.44</v>
+        <v>7.5</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
@@ -1194,20 +1295,20 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>3.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>1.1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="n">
@@ -1225,7 +1326,7 @@
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>VARGUS_8SI02</t>
+          <t>VARGUS_6SI02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -1267,6 +1368,25 @@
       <c r="AQ6" t="inlineStr">
         <is>
           <t>Full MAIN VARDEX 2022-METRIC.pdf</t>
+        </is>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>108.54</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>9538.780000000001</v>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
         </is>
       </c>
     </row>
